--- a/BELTRAN 34/Libro1.xlsx
+++ b/BELTRAN 34/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELTRAN 34\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1985DBF-3947-4289-A6FA-A45A940E2E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E630DC9A-3A7C-44E5-8B31-0CCD6C7BF1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40F7CB68-AA62-4B90-B02B-2F8168283C84}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="9">
   <si>
     <t>DESGLOSE DEUDA - UF 1 - Local 1/ Entrep. - BELTRAN 34</t>
   </si>
@@ -38,6 +38,21 @@
   <si>
     <t>Expensas Extraord.</t>
   </si>
+  <si>
+    <t>Interes</t>
+  </si>
+  <si>
+    <t>TOTALES:</t>
+  </si>
+  <si>
+    <t>TOTAL EXPENSAS:</t>
+  </si>
+  <si>
+    <t>TOTAL INTERESES</t>
+  </si>
+  <si>
+    <t>TOTAL:</t>
+  </si>
 </sst>
 </file>
 
@@ -46,7 +61,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,8 +84,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -80,12 +103,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -109,31 +126,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -449,34 +471,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A0868C-F56B-4272-A7E5-AB78808DF362}">
-  <dimension ref="E4:J51"/>
+  <dimension ref="E4:K59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E4" s="2" t="s">
+    <row r="4" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="6" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="6" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E7" s="3">
+      <c r="F6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="K6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E7" s="1">
         <v>45658</v>
       </c>
       <c r="F7" s="4">
@@ -487,22 +518,29 @@
         <v>23892</v>
       </c>
       <c r="I7" s="4"/>
-    </row>
-    <row r="10" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="8">
+        <f>(F7+H7)*3%</f>
+        <v>2019.96</v>
+      </c>
+    </row>
+    <row r="10" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E11" s="3">
+      <c r="F10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="K10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E11" s="1">
         <f>E7+31</f>
         <v>45689</v>
       </c>
@@ -514,22 +552,29 @@
         <v>23892</v>
       </c>
       <c r="I11" s="4"/>
-    </row>
-    <row r="14" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="K11" s="8">
+        <f>(F11+H11)*3%</f>
+        <v>2345.7599999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E14" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E15" s="3">
+      <c r="F14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="K14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E15" s="1">
         <f>E11+31</f>
         <v>45720</v>
       </c>
@@ -541,22 +586,29 @@
         <v>23892</v>
       </c>
       <c r="I15" s="4"/>
-    </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="K15" s="8">
+        <f>(F15+H15)*3%</f>
+        <v>2834.46</v>
+      </c>
+    </row>
+    <row r="18" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E18" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E19" s="3">
+      <c r="F18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="K18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E19" s="1">
         <f>E15+31</f>
         <v>45751</v>
       </c>
@@ -564,24 +616,31 @@
         <v>86880</v>
       </c>
       <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="22" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="K19" s="8">
+        <f>(F19+H19)*3%</f>
+        <v>2606.4</v>
+      </c>
+    </row>
+    <row r="22" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E22" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E23" s="3">
+      <c r="F22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="K22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E23" s="1">
         <f>E19+31</f>
         <v>45782</v>
       </c>
@@ -589,49 +648,63 @@
         <v>86880</v>
       </c>
       <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="26" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="K23" s="8">
+        <f>(F23+H23)*3%</f>
+        <v>2606.4</v>
+      </c>
+    </row>
+    <row r="26" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E26" t="s">
         <v>1</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E27" s="3">
+      <c r="F26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="K26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E27" s="1">
         <f>E23+31</f>
         <v>45813</v>
       </c>
-      <c r="F27" s="9">
-        <v>977740</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="30" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F27" s="5">
+        <v>97740</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="K27" s="8">
+        <f>(F27+H27)*3%</f>
+        <v>2932.2</v>
+      </c>
+    </row>
+    <row r="30" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E30" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E31" s="3">
+      <c r="F30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="K30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E31" s="1">
         <f>E27+31</f>
         <v>45844</v>
       </c>
@@ -639,76 +712,99 @@
         <v>55903.81</v>
       </c>
       <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="K31" s="8">
+        <f>(F31+H31)*3%</f>
+        <v>1677.1143</v>
+      </c>
+    </row>
+    <row r="33" spans="5:11" x14ac:dyDescent="0.3">
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E34" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I34" s="5"/>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E35" s="3">
+      <c r="F34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="K34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E35" s="1">
         <f>E31+31</f>
         <v>45875</v>
       </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-    </row>
-    <row r="38" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F35" s="5">
+        <v>124890</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="K35" s="8">
+        <f>(F35+H35)*3%</f>
+        <v>3746.7</v>
+      </c>
+    </row>
+    <row r="38" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E38" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="5"/>
-    </row>
-    <row r="39" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E39" s="3">
+      <c r="F38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="K38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E39" s="1">
         <f>E35+31</f>
         <v>45906</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-    </row>
-    <row r="42" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="K39" s="8">
+        <f>(F39+H39)*3%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E42" t="s">
         <v>1</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E43" s="3">
+      <c r="F42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="2"/>
+      <c r="K42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E43" s="1">
         <f>E39+31</f>
         <v>45937</v>
       </c>
@@ -716,24 +812,31 @@
         <v>106428</v>
       </c>
       <c r="G43" s="4"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="46" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="K43" s="8">
+        <f>(F43+H43)*3%</f>
+        <v>3192.8399999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E46" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E47" s="3">
+      <c r="F46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="K46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E47" s="1">
         <f>E43+31</f>
         <v>45968</v>
       </c>
@@ -741,51 +844,108 @@
         <v>157470</v>
       </c>
       <c r="G47" s="4"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="50" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="K47" s="8">
+        <f>(F47+H47)*3%</f>
+        <v>4724.0999999999995</v>
+      </c>
+    </row>
+    <row r="50" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E50" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="5:9" x14ac:dyDescent="0.3">
-      <c r="E51" s="3">
+      <c r="F50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="2"/>
+      <c r="K50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E51" s="1">
         <f>E47+31</f>
         <v>45999</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="K51" s="8">
+        <f>(F51+H51)*3%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="E56" s="9">
+        <f>F7+H7+H11+F11+F15+H15+H19+F19+F23+H23+H27+F27+F31+H35+F35+H32+H31+H39+F39+F43+H43+H47+F47+F51+H51</f>
+        <v>956197.81</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9">
+        <f>SUM(K7:K51)</f>
+        <v>28685.934300000001</v>
+      </c>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+    </row>
+    <row r="58" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="G58" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="G59" s="11">
+        <f>E56+H56</f>
+        <v>984883.74430000002</v>
+      </c>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H30:I30"/>
+  <mergeCells count="53">
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="G59:I59"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="F47:G47"/>
     <mergeCell ref="F51:G51"/>
@@ -802,23 +962,25 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/BELTRAN 34/Libro1.xlsx
+++ b/BELTRAN 34/Libro1.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELTRAN 34\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELTRAN 34\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E630DC9A-3A7C-44E5-8B31-0CCD6C7BF1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1AC4C6-BE0D-4842-9796-A44621CFA4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40F7CB68-AA62-4B90-B02B-2F8168283C84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{40F7CB68-AA62-4B90-B02B-2F8168283C84}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$E$4:$K$60</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -126,36 +129,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -471,482 +479,501 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78A0868C-F56B-4272-A7E5-AB78808DF362}">
-  <dimension ref="E4:K59"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="C4:K59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="0.140625" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E4" s="6" t="s">
+    <row r="4" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="6" spans="5:11" x14ac:dyDescent="0.3">
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="6" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="2"/>
+      <c r="F6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5"/>
       <c r="K6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E7" s="1">
         <v>45658</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="10">
         <v>43440</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10">
         <v>23892</v>
       </c>
-      <c r="I7" s="4"/>
-      <c r="K7" s="8">
+      <c r="I7" s="10"/>
+      <c r="K7" s="3">
         <f>(F7+H7)*3%</f>
         <v>2019.96</v>
       </c>
     </row>
-    <row r="10" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="2"/>
+      <c r="F10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="5"/>
       <c r="K10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E11" s="1">
         <f>E7+31</f>
         <v>45689</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="10">
         <v>54300</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4">
+      <c r="G11" s="10"/>
+      <c r="H11" s="10">
         <v>23892</v>
       </c>
-      <c r="I11" s="4"/>
-      <c r="K11" s="8">
+      <c r="I11" s="10"/>
+      <c r="K11" s="3">
         <f>(F11+H11)*3%</f>
         <v>2345.7599999999998</v>
       </c>
     </row>
-    <row r="14" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="2"/>
+      <c r="F14" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="5"/>
       <c r="K14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E15" s="1">
         <f>E11+31</f>
         <v>45720</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="10">
         <v>70590</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4">
+      <c r="G15" s="10"/>
+      <c r="H15" s="10">
         <v>23892</v>
       </c>
-      <c r="I15" s="4"/>
-      <c r="K15" s="8">
+      <c r="I15" s="10"/>
+      <c r="K15" s="3">
         <f>(F15+H15)*3%</f>
         <v>2834.46</v>
       </c>
     </row>
-    <row r="18" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="2"/>
+      <c r="F18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="5"/>
       <c r="K18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E19" s="1">
         <f>E15+31</f>
         <v>45751</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="10">
         <v>86880</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="K19" s="8">
+      <c r="G19" s="10"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="K19" s="3">
         <f>(F19+H19)*3%</f>
         <v>2606.4</v>
       </c>
     </row>
-    <row r="22" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2"/>
+      <c r="F22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5"/>
       <c r="K22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E23" s="1">
         <f>E19+31</f>
         <v>45782</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="10">
         <v>86880</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="K23" s="8">
+      <c r="G23" s="10"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="K23" s="3">
         <f>(F23+H23)*3%</f>
         <v>2606.4</v>
       </c>
     </row>
-    <row r="26" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
         <v>1</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3"/>
+      <c r="F26" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="8"/>
       <c r="K26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E27" s="1">
         <f>E23+31</f>
         <v>45813</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="9">
         <v>97740</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="K27" s="8">
+      <c r="G27" s="9"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="K27" s="3">
         <f>(F27+H27)*3%</f>
         <v>2932.2</v>
       </c>
     </row>
-    <row r="30" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E30" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="2"/>
+      <c r="F30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="5"/>
       <c r="K30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E31" s="1">
         <f>E27+31</f>
         <v>45844</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="10">
         <v>55903.81</v>
       </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="K31" s="8">
+      <c r="G31" s="10"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="K31" s="3">
         <f>(F31+H31)*3%</f>
         <v>1677.1143</v>
       </c>
     </row>
-    <row r="33" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-    </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E34" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I34" s="3"/>
+      <c r="F34" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="8"/>
       <c r="K34" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E35" s="1">
         <f>E31+31</f>
         <v>45875</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="9">
         <v>124890</v>
       </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="K35" s="8">
+      <c r="G35" s="9"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="K35" s="3">
         <f>(F35+H35)*3%</f>
         <v>3746.7</v>
       </c>
     </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E38" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="3"/>
+      <c r="F38" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="8"/>
       <c r="K38" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E39" s="1">
         <f>E35+31</f>
         <v>45906</v>
       </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="K39" s="8">
+      <c r="F39" s="9">
+        <v>106528</v>
+      </c>
+      <c r="G39" s="9"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="K39" s="3">
         <f>(F39+H39)*3%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="5:11" x14ac:dyDescent="0.3">
+        <v>3195.8399999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E42" t="s">
         <v>1</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="2"/>
+      <c r="F42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="5"/>
       <c r="K42" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E43" s="1">
         <f>E39+31</f>
         <v>45937</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="10">
         <v>106428</v>
       </c>
-      <c r="G43" s="4"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="K43" s="8">
+      <c r="G43" s="10"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="K43" s="3">
         <f>(F43+H43)*3%</f>
         <v>3192.8399999999997</v>
       </c>
     </row>
-    <row r="46" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E46" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="2"/>
+      <c r="F46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="5"/>
       <c r="K46" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E47" s="1">
         <f>E43+31</f>
         <v>45968</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="10">
         <v>157470</v>
       </c>
-      <c r="G47" s="4"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="K47" s="8">
+      <c r="G47" s="10"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="K47" s="3">
         <f>(F47+H47)*3%</f>
         <v>4724.0999999999995</v>
       </c>
     </row>
-    <row r="50" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E50" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I50" s="2"/>
+      <c r="F50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="5"/>
       <c r="K50" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="5:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E51" s="1">
         <f>E47+31</f>
         <v>45999</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="K51" s="8">
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="K51" s="3">
         <f>(F51+H51)*3%</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E54" t="s">
+    <row r="54" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E54" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E55" t="s">
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+    </row>
+    <row r="55" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E55" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E56" s="9">
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E56" s="4">
         <f>F7+H7+H11+F11+F15+H15+H19+F19+F23+H23+H27+F27+F31+H35+F35+H32+H31+H39+F39+F43+H43+H47+F47+F51+H51</f>
-        <v>956197.81</v>
-      </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9">
+        <v>1062725.81</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4">
         <f>SUM(K7:K51)</f>
-        <v>28685.934300000001</v>
-      </c>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-    </row>
-    <row r="58" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G58" s="12" t="s">
+        <v>31881.774300000001</v>
+      </c>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+    </row>
+    <row r="58" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E58" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G59" s="11">
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" spans="5:11" x14ac:dyDescent="0.25">
+      <c r="E59" s="12">
         <f>E56+H56</f>
-        <v>984883.74430000002</v>
-      </c>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
+        <v>1094607.5843</v>
+      </c>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="H56:J56"/>
-    <mergeCell ref="G59:I59"/>
-    <mergeCell ref="E4:K4"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F43:G43"/>
+  <mergeCells count="56">
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="E58:J58"/>
+    <mergeCell ref="E59:J59"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="F47:G47"/>
     <mergeCell ref="F51:G51"/>
     <mergeCell ref="H6:I6"/>
@@ -963,24 +990,28 @@
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="E4:K4"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F35:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>